--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_09-07-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_09-07-2025.xlsx
@@ -945,7 +945,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£23.86</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.78</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.28</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.25</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.78</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
